--- a/AAII_Financials/Quarterly/BAK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>BAK</t>
   </si>
@@ -656,174 +656,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4191400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2968900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2923200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3246000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3277200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3394100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3096600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3905100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3435900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3572900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3439800</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3165500</v>
+      </c>
+      <c r="E9" s="3">
         <v>2758100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2690800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3164100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3210800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3165600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2911100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3492100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3185600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3331500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3232100</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1025900</v>
+      </c>
+      <c r="E10" s="3">
         <v>210900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>232400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>81800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>66400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>228500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>185500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>413000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>250400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>241500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>207700</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -837,43 +850,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E12" s="3">
         <v>19600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>19100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>22700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>20000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>21100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -907,78 +924,87 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
         <v>22000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>389600</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
         <v>-5800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22600</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3800</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>177400</v>
+      </c>
+      <c r="E15" s="3">
         <v>183100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>163400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>158200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>184600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>163400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>135200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>184400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>177100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>185600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>173500</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,78 +1015,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3464100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2999600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2485700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3559300</v>
       </c>
-      <c r="G17" s="3">
-        <v>3375600</v>
-      </c>
       <c r="H17" s="3">
+        <v>3456000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3381400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3380700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3719600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3455400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3576300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3651500</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>727300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-30700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>437500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-313400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-98400</v>
-      </c>
       <c r="H18" s="3">
+        <v>-178800</v>
+      </c>
+      <c r="I18" s="3">
         <v>12700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-284100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>185500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-211700</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,183 +1107,199 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-221000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-465200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-101300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-55200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-177800</v>
-      </c>
       <c r="H20" s="3">
+        <v>-333800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-313100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>772500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>216000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>908000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>252800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1125700</v>
+      </c>
+      <c r="E21" s="3">
         <v>617600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>702300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-100000</v>
       </c>
-      <c r="G21" s="3">
-        <v>264100</v>
-      </c>
       <c r="H21" s="3">
+        <v>339700</v>
+      </c>
+      <c r="I21" s="3">
         <v>489200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-921400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>153900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-750400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-70600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-47600</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>311500</v>
+      </c>
+      <c r="E22" s="3">
         <v>255900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>273200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>300000</v>
       </c>
-      <c r="G22" s="3">
-        <v>216700</v>
-      </c>
       <c r="H22" s="3">
+        <v>303600</v>
+      </c>
+      <c r="I22" s="3">
         <v>225900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>309600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>291300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>211500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>224300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>259300</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>687300</v>
+      </c>
+      <c r="E23" s="3">
         <v>182700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-98000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-486200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-97300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>142300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1346700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-241100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1084400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-412900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-376300</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-56200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1904300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-453500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-25700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>32100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-394800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-81500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-380800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-135800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-15500</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1333,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>641400</v>
+      </c>
+      <c r="E26" s="3">
         <v>238800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2002400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-32600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-71600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>110200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-951800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-159600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-703600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-277100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-360900</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>641800</v>
+      </c>
+      <c r="E27" s="3">
         <v>277200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1867300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-49000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>121700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-913000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-108900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-672800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-268200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-324600</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1447,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1485,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,78 +1561,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>221000</v>
+      </c>
+      <c r="E32" s="3">
         <v>465200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>101300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>55200</v>
       </c>
-      <c r="G32" s="3">
-        <v>177800</v>
-      </c>
       <c r="H32" s="3">
+        <v>333800</v>
+      </c>
+      <c r="I32" s="3">
         <v>313100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-772500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-216000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-908000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-252800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>641800</v>
+      </c>
+      <c r="E33" s="3">
         <v>277200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1867300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-49000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>121700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-913000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-108900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-672800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-268200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-324600</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1675,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>641800</v>
+      </c>
+      <c r="E35" s="3">
         <v>277200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1867300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-49000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>121700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-913000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-108900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-672800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-268200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-324600</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,323 +1790,351 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>758800</v>
+      </c>
+      <c r="E41" s="3">
         <v>896700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1906500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1250200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1685300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1973800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2423000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2188900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2560200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2834200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2923800</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>385500</v>
+      </c>
+      <c r="E42" s="3">
         <v>262200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>242600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>139800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>205700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>298600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>288800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>444100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>561300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>789600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1021400</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1903600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1315200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1208100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>965600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1082600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>983900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>924200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>958100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1112800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1177200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1160100</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2562300</v>
+      </c>
+      <c r="E44" s="3">
         <v>2160900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1892000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2373400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2476900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2513600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2213100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2561500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2417000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2643000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2582700</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E45" s="3">
         <v>385500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>278900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>191600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>177700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>139200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>140300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>147300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>149700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28200</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5655500</v>
+      </c>
+      <c r="E46" s="3">
         <v>5020600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5528000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4929800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5642200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5947700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5988300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6292900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6798600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7593700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7716100</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E47" s="3">
         <v>104300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>95000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>103800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>102400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>87600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>78300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>116400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>34300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>37700</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7692600</v>
+      </c>
+      <c r="E48" s="3">
         <v>7590400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7527800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7805200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7709200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7376500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7136100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7626500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7801400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8465200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8702100</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>574800</v>
+      </c>
+      <c r="E49" s="3">
         <v>575500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>556100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>569500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>588800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>578500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>547600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>586200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>585400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>621900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>640500</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2206,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>962600</v>
+      </c>
+      <c r="E52" s="3">
         <v>926800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>876000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>503100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>586700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>476300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>428300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>489400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>437900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>482100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>482500</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2282,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15294900</v>
+      </c>
+      <c r="E54" s="3">
         <v>14543600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14865500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16396400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16756500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16642900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16423100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17015000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17501600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18650600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18906700</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,218 +2354,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2084600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2156700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2392300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2602900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2874600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2766400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2729700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2852600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2986300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2970600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2724700</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4281000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3954600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3935000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>551300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>684900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>606600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>668600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>641300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>696200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>630400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>772000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>675200</v>
+      </c>
+      <c r="E59" s="3">
         <v>665600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>741100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>768900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>889000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>917200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>904800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1157500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1307400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1321500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1300800</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7335000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7075100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7301700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4194100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4674600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4517500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4571100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4913300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5209100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5211200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5047900</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8901700</v>
+      </c>
+      <c r="E61" s="3">
         <v>9012900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9012700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11314400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11312200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11423700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11251100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11239600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11351500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11536400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11574500</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1200200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1188500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1188900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1072300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1063200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>992100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>813000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>865300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>957600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1146100</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2694,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17821000</v>
+      </c>
+      <c r="E66" s="3">
         <v>17655300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17861500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16991800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17354500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17304800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17114700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17289200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17743900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18178400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18230900</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2900,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3689200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4304600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-4339500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2555800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2495400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2325500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2269100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1543200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1475800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-813700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-564300</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3052,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2429400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-3016500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2931600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-662900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-698300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-738800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-773200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-4600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-53000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>614700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>822700</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3128,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>641800</v>
+      </c>
+      <c r="E81" s="3">
         <v>277200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1867300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-49000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>121700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-913000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-108900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-672800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-268200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-324600</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3227,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>221300</v>
+      </c>
+      <c r="E83" s="3">
         <v>202700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>178700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>231900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>227000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>239900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>279900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>240500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>274600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>237400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>249300</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3453,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-814500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-163400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-128200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-52300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-406700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>131900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-145100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>260100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>192400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>208800</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3509,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-108900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-125600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-95000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-237900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-118900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-113900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-167000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-154100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-183600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-173500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-254100</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3621,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-162300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-176400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-112200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-198300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-127700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-164400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-115500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-174400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-173700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-245700</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3677,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3464,23 +3698,26 @@
       <c r="H96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>900</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +3827,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-69600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>932600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-137400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-190700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-33300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>385900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-117000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-183200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-52600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>173700</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-99400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>142400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-43700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>97100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>39500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-23500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>29600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-65500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-14400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-36100</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-144200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1116200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>696800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-472800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-391600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-639900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>495900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-421300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>113300</v>
       </c>
     </row>
